--- a/AuxiliaryTool.Avalonia/AuxiliaryTool.Avalonia/Assets/ExamA01Score.xlsx
+++ b/AuxiliaryTool.Avalonia/AuxiliaryTool.Avalonia/Assets/ExamA01Score.xlsx
@@ -2876,7 +2876,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>阿虚</t>
+          <t>佐佐木</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -18847,7 +18847,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>阿虚</t>
+          <t>佐佐木</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -32515,7 +32515,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>阿虚</t>
+          <t>佐佐木</t>
         </is>
       </c>
       <c r="B16" t="n">
